--- a/колонки таблиц.xlsx
+++ b/колонки таблиц.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B181C1-868A-439B-A756-17C26F3D34A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC02AD9C-5BB9-454C-849B-31342C70959B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19970" uniqueCount="2422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21320" uniqueCount="2798">
   <si>
     <t>TABLE_NAME</t>
   </si>
@@ -7323,6 +7323,1134 @@
   </si>
   <si>
     <t>Группа объектов страхования (ссылка на bps_request_ins_task_insured_obj.id)</t>
+  </si>
+  <si>
+    <t>bps_corporate_claim</t>
+  </si>
+  <si>
+    <t>Модель данных по Убытки ДКС (corporate_claim)</t>
+  </si>
+  <si>
+    <t>calc_remains_ins_sum</t>
+  </si>
+  <si>
+    <t>Расчет остатка СС</t>
+  </si>
+  <si>
+    <t>n_contract</t>
+  </si>
+  <si>
+    <t>franchise</t>
+  </si>
+  <si>
+    <t>Франшиза</t>
+  </si>
+  <si>
+    <t>d_sign_contract</t>
+  </si>
+  <si>
+    <t>d_start_contract</t>
+  </si>
+  <si>
+    <t>Дата начала страхования</t>
+  </si>
+  <si>
+    <t>d_end_contract</t>
+  </si>
+  <si>
+    <t>Дата окончания действия договора</t>
+  </si>
+  <si>
+    <t>is_ruble_loss</t>
+  </si>
+  <si>
+    <t>Рублевый убыток</t>
+  </si>
+  <si>
+    <t>ins_type</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>Валюта договора</t>
+  </si>
+  <si>
+    <t>gross_premium</t>
+  </si>
+  <si>
+    <t>Начисленная премия</t>
+  </si>
+  <si>
+    <t>paid_premium</t>
+  </si>
+  <si>
+    <t>Оплаченная премия</t>
+  </si>
+  <si>
+    <t>kind_of_franchise</t>
+  </si>
+  <si>
+    <t>Вид франшизы</t>
+  </si>
+  <si>
+    <t>franchise_type</t>
+  </si>
+  <si>
+    <t>franchise_summ</t>
+  </si>
+  <si>
+    <t>not_found</t>
+  </si>
+  <si>
+    <t>ins_persone_count</t>
+  </si>
+  <si>
+    <t>obj_address</t>
+  </si>
+  <si>
+    <t>input_doc_num</t>
+  </si>
+  <si>
+    <t>№ Вх документа</t>
+  </si>
+  <si>
+    <t>assitans_partner_id</t>
+  </si>
+  <si>
+    <t>Партнёр (ссылка на base_service_organization.id)</t>
+  </si>
+  <si>
+    <t>loss_curator_legal_support_id</t>
+  </si>
+  <si>
+    <t>Куратор убытка (правовое сопровождение) (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>id_tsunami</t>
+  </si>
+  <si>
+    <t>Внешний ID убытка</t>
+  </si>
+  <si>
+    <t>status_tsunami</t>
+  </si>
+  <si>
+    <t>Статус цунами</t>
+  </si>
+  <si>
+    <t>appliant_status</t>
+  </si>
+  <si>
+    <t>Статус заявителя</t>
+  </si>
+  <si>
+    <t>appliant_id</t>
+  </si>
+  <si>
+    <t>Заявитель (ссылка на bps_contractor.id)</t>
+  </si>
+  <si>
+    <t>d_sent_application_sk</t>
+  </si>
+  <si>
+    <t>comment_terms</t>
+  </si>
+  <si>
+    <t>Комментарий по заявлению</t>
+  </si>
+  <si>
+    <t>insured_event_description</t>
+  </si>
+  <si>
+    <t>Описание страхового случая</t>
+  </si>
+  <si>
+    <t>is_without_references</t>
+  </si>
+  <si>
+    <t>is_damaged_prop_insured_in_other_ic</t>
+  </si>
+  <si>
+    <t>Поврежденное имущество застраховано в другой СК</t>
+  </si>
+  <si>
+    <t>other_ic_name</t>
+  </si>
+  <si>
+    <t>Название другой СК</t>
+  </si>
+  <si>
+    <t>possible_culprit_data</t>
+  </si>
+  <si>
+    <t>Данные предполагаемого виновника</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>E-mail Заявителя</t>
+  </si>
+  <si>
+    <t>missing_applicant_contacts</t>
+  </si>
+  <si>
+    <t>Контакты отсутствуют в карточке контрагента</t>
+  </si>
+  <si>
+    <t>other_mobile_phone</t>
+  </si>
+  <si>
+    <t>Иной телефон Заявителя</t>
+  </si>
+  <si>
+    <t>other_email</t>
+  </si>
+  <si>
+    <t>Иной e-mail Заявителя</t>
+  </si>
+  <si>
+    <t>other_applicant_address</t>
+  </si>
+  <si>
+    <t>Иной почтовый адрес заявителя</t>
+  </si>
+  <si>
+    <t>risk</t>
+  </si>
+  <si>
+    <t>Описание риска</t>
+  </si>
+  <si>
+    <t>reimbursement_method_motor</t>
+  </si>
+  <si>
+    <t>ins_event_type</t>
+  </si>
+  <si>
+    <t>Вид события</t>
+  </si>
+  <si>
+    <t>d_claim</t>
+  </si>
+  <si>
+    <t>Дата заявления</t>
+  </si>
+  <si>
+    <t>d_case</t>
+  </si>
+  <si>
+    <t>t_case</t>
+  </si>
+  <si>
+    <t>time without time zone</t>
+  </si>
+  <si>
+    <t>Время события</t>
+  </si>
+  <si>
+    <t>tsunami_appeal_num</t>
+  </si>
+  <si>
+    <t>Номер претензии Цунами</t>
+  </si>
+  <si>
+    <t>insurance_object_number</t>
+  </si>
+  <si>
+    <t>Номер объекта страхования</t>
+  </si>
+  <si>
+    <t>d_insurance_object</t>
+  </si>
+  <si>
+    <t>Дата объекта страхования</t>
+  </si>
+  <si>
+    <t>carriage_num</t>
+  </si>
+  <si>
+    <t>Номер вагона</t>
+  </si>
+  <si>
+    <t>d_contract_payment</t>
+  </si>
+  <si>
+    <t>Дата оплаты договора Клиентом</t>
+  </si>
+  <si>
+    <t>d_get_documents</t>
+  </si>
+  <si>
+    <t>Дата получения посл. док-та от клиента</t>
+  </si>
+  <si>
+    <t>is_appeal_without_reference</t>
+  </si>
+  <si>
+    <t>Обращение "Без справок"</t>
+  </si>
+  <si>
+    <t>currency_settlement_date</t>
+  </si>
+  <si>
+    <t>Дата расчета валюты</t>
+  </si>
+  <si>
+    <t>is_quick_settlement</t>
+  </si>
+  <si>
+    <t>Быстрое урегулирование</t>
+  </si>
+  <si>
+    <t>cargo_condition</t>
+  </si>
+  <si>
+    <t>События обнаружения груза</t>
+  </si>
+  <si>
+    <t>in_channel</t>
+  </si>
+  <si>
+    <t>spec_equipment_type</t>
+  </si>
+  <si>
+    <t>Тип спецтехники</t>
+  </si>
+  <si>
+    <t>mark_model_custom_text</t>
+  </si>
+  <si>
+    <t>Наименование, марка/модель</t>
+  </si>
+  <si>
+    <t>chassis_body_num</t>
+  </si>
+  <si>
+    <t>Номер шасси/кузова</t>
+  </si>
+  <si>
+    <t>factory_num</t>
+  </si>
+  <si>
+    <t>Заводской/регистрационный номер</t>
+  </si>
+  <si>
+    <t>issue_year</t>
+  </si>
+  <si>
+    <t>Год выпуска</t>
+  </si>
+  <si>
+    <t>address_kladr_ins_event_id</t>
+  </si>
+  <si>
+    <t>Адрес по кладр (ссылка на base_kladr.id)</t>
+  </si>
+  <si>
+    <t>is_not_kladr_ins_event</t>
+  </si>
+  <si>
+    <t>Адрес не найден по КЛАДР/ФИАС</t>
+  </si>
+  <si>
+    <t>region_ins_event</t>
+  </si>
+  <si>
+    <t>city_ins_event</t>
+  </si>
+  <si>
+    <t>Город или населенный пункт</t>
+  </si>
+  <si>
+    <t>street_ins_event</t>
+  </si>
+  <si>
+    <t>house_ins_event</t>
+  </si>
+  <si>
+    <t>housing_ins_event</t>
+  </si>
+  <si>
+    <t>apartment_ins_event</t>
+  </si>
+  <si>
+    <t>character varying(15)</t>
+  </si>
+  <si>
+    <t>postcode_ins_event</t>
+  </si>
+  <si>
+    <t>place_ins_event</t>
+  </si>
+  <si>
+    <t>Адрес места события строкой</t>
+  </si>
+  <si>
+    <t>fias_address</t>
+  </si>
+  <si>
+    <t>loss_risk</t>
+  </si>
+  <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>claim_cancel_reason</t>
+  </si>
+  <si>
+    <t>Причина аннулирования требования</t>
+  </si>
+  <si>
+    <t>subrogation</t>
+  </si>
+  <si>
+    <t>Регресс</t>
+  </si>
+  <si>
+    <t>regress_basis</t>
+  </si>
+  <si>
+    <t>Основание для суброгации</t>
+  </si>
+  <si>
+    <t>loss_sum</t>
+  </si>
+  <si>
+    <t>Размер заявленного убытка в валюте расходов</t>
+  </si>
+  <si>
+    <t>s_claim_usd</t>
+  </si>
+  <si>
+    <t>Размер заявленного убытка в валюте</t>
+  </si>
+  <si>
+    <t>s_claim_curr_expense</t>
+  </si>
+  <si>
+    <t>Сумма выплаты в валюте расходов</t>
+  </si>
+  <si>
+    <t>s_claim_curr_contract</t>
+  </si>
+  <si>
+    <t>Сумма выплаты в валюте</t>
+  </si>
+  <si>
+    <t>rzu_with_franchise_rub</t>
+  </si>
+  <si>
+    <t>РЗУ с учетом франшизы, руб.</t>
+  </si>
+  <si>
+    <t>rzu_with_franchise_expense_currency</t>
+  </si>
+  <si>
+    <t>РЗУ с учетом франшизы, в валюте расходов</t>
+  </si>
+  <si>
+    <t>rzu_with_franchise_contract_currency</t>
+  </si>
+  <si>
+    <t>РЗУ с учетом франшизы в валюте</t>
+  </si>
+  <si>
+    <t>s_reject</t>
+  </si>
+  <si>
+    <t>reject_reason</t>
+  </si>
+  <si>
+    <t>compensation_form</t>
+  </si>
+  <si>
+    <t>compensation_type</t>
+  </si>
+  <si>
+    <t>d_decision</t>
+  </si>
+  <si>
+    <t>d_close</t>
+  </si>
+  <si>
+    <t>Дата урегулирования</t>
+  </si>
+  <si>
+    <t>d_pay_plan</t>
+  </si>
+  <si>
+    <t>Дата выплаты (план)</t>
+  </si>
+  <si>
+    <t>payment_form_dr</t>
+  </si>
+  <si>
+    <t>d_reject_notify_plan</t>
+  </si>
+  <si>
+    <t>Дата уведомления об отказе (план)</t>
+  </si>
+  <si>
+    <t>is_ombudsman_proceed</t>
+  </si>
+  <si>
+    <t>ФУ убыток</t>
+  </si>
+  <si>
+    <t>is_execut_proceed</t>
+  </si>
+  <si>
+    <t>Судебный убыток</t>
+  </si>
+  <si>
+    <t>user_approve_id</t>
+  </si>
+  <si>
+    <t>Утверждающий (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>loss_currency</t>
+  </si>
+  <si>
+    <t>Валюта расходов</t>
+  </si>
+  <si>
+    <t>curr_exchange</t>
+  </si>
+  <si>
+    <t>Курс валюты расходов к валюте договора</t>
+  </si>
+  <si>
+    <t>currency_exch_rate_contract_to_rub</t>
+  </si>
+  <si>
+    <t>Курс валюты договора к рублю</t>
+  </si>
+  <si>
+    <t>curr_rate_to_rub_on_date_decision</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>ustification_reject_reason</t>
+  </si>
+  <si>
+    <t>Обоснование причин отказа</t>
+  </si>
+  <si>
+    <t>revise_ins_regulation</t>
+  </si>
+  <si>
+    <t>Редакция Правил</t>
+  </si>
+  <si>
+    <t>is_expiration</t>
+  </si>
+  <si>
+    <t>Истечение срока рассмотрения</t>
+  </si>
+  <si>
+    <t>subrogation_confirmed</t>
+  </si>
+  <si>
+    <t>lack_subrogation_reason</t>
+  </si>
+  <si>
+    <t>Причина отсутствия суброгации</t>
+  </si>
+  <si>
+    <t>go_price</t>
+  </si>
+  <si>
+    <t>d_control</t>
+  </si>
+  <si>
+    <t>Контрольная дата</t>
+  </si>
+  <si>
+    <t>is_constructive_death</t>
+  </si>
+  <si>
+    <t>pay_reason</t>
+  </si>
+  <si>
+    <t>Обоснование выплаты</t>
+  </si>
+  <si>
+    <t>n_loss</t>
+  </si>
+  <si>
+    <t>Номер требования</t>
+  </si>
+  <si>
+    <t>payment_form</t>
+  </si>
+  <si>
+    <t>Форма оплаты</t>
+  </si>
+  <si>
+    <t>num_id</t>
+  </si>
+  <si>
+    <t>Номер текущей нумерации</t>
+  </si>
+  <si>
+    <t>Куратор требования (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>s_pay_saved</t>
+  </si>
+  <si>
+    <t>Сумма выплаты для истории</t>
+  </si>
+  <si>
+    <t>not_in_mssql</t>
+  </si>
+  <si>
+    <t>claim_id</t>
+  </si>
+  <si>
+    <t>Заявление (ссылка на bps_claim.id)</t>
+  </si>
+  <si>
+    <t>callcenter_message_id</t>
+  </si>
+  <si>
+    <t>Заявка, из которой создан этот документ (ссылка на bps_callcenter_message.id)</t>
+  </si>
+  <si>
+    <t>parent_damage_request_id</t>
+  </si>
+  <si>
+    <t>Родительское требование (ссылка на bps_damage_request.id)</t>
+  </si>
+  <si>
+    <t>ecm_id</t>
+  </si>
+  <si>
+    <t>character varying(36)</t>
+  </si>
+  <si>
+    <t>tsunami_status</t>
+  </si>
+  <si>
+    <t>Результат загрузки в Цунами</t>
+  </si>
+  <si>
+    <t>pm_curator_id</t>
+  </si>
+  <si>
+    <t>ПМ/Куратор убытка (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>sms_notification_payment</t>
+  </si>
+  <si>
+    <t>Уведомление о оплате (успешной или отказе) отправлено</t>
+  </si>
+  <si>
+    <t>is_need_recreate_ins_act</t>
+  </si>
+  <si>
+    <t>Нужно ли пересоздать страховой акт</t>
+  </si>
+  <si>
+    <t>need_sms_send_type</t>
+  </si>
+  <si>
+    <t>Тип смс, которое нужно отправить</t>
+  </si>
+  <si>
+    <t>currency_exch_rate_auto_filled</t>
+  </si>
+  <si>
+    <t>Флаг, означающий, что курс загружен с апи цб рф</t>
+  </si>
+  <si>
+    <t>curr_rate_to_rub_on_date_decision_auto_filled</t>
+  </si>
+  <si>
+    <t>Флаг, означающий, что курс на дату принятия решения загружен с апи цб рф</t>
+  </si>
+  <si>
+    <t>curr_exchange_auto_filled</t>
+  </si>
+  <si>
+    <t>Флаг, означающий, что Курс валюты расходов к валюте договора загружен с апи цб рф</t>
+  </si>
+  <si>
+    <t>is_try_get_decison_model</t>
+  </si>
+  <si>
+    <t>Флаг, попытки поиска подходящей настройки DecisionMakeModel</t>
+  </si>
+  <si>
+    <t>last_registration_author_id</t>
+  </si>
+  <si>
+    <t>Автор регистрации последнего перехода (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>d_last_registration_event</t>
+  </si>
+  <si>
+    <t>Дата регистрации последнего перехода</t>
+  </si>
+  <si>
+    <t>appeal_to_erkc</t>
+  </si>
+  <si>
+    <t>Обращение в ЕРКЦ</t>
+  </si>
+  <si>
+    <t>child_task_sended_notification_states_ids</t>
+  </si>
+  <si>
+    <t>Этапы и ID дочерних задач с уведомлениями о переходе</t>
+  </si>
+  <si>
+    <t>external_ecm_id</t>
+  </si>
+  <si>
+    <t>ИД внешнего документа в ЕСМ</t>
+  </si>
+  <si>
+    <t>convention_type</t>
+  </si>
+  <si>
+    <t>d_death_decision</t>
+  </si>
+  <si>
+    <t>Дата принятия решения о гибели</t>
+  </si>
+  <si>
+    <t>d_receipt_money_in_sk</t>
+  </si>
+  <si>
+    <t>Дата реализации ГОИ</t>
+  </si>
+  <si>
+    <t>goi_price</t>
+  </si>
+  <si>
+    <t>Стоимость ГОИ</t>
+  </si>
+  <si>
+    <t>gots_in_sk_client</t>
+  </si>
+  <si>
+    <t>ГОИ в СК/Клиент</t>
+  </si>
+  <si>
+    <t>payment_decision</t>
+  </si>
+  <si>
+    <t>Решение о выплате по КГ</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>parent_corporate_claim_id</t>
+  </si>
+  <si>
+    <t>Родительское требование (ссылка на bps_corporate_claim.id)</t>
+  </si>
+  <si>
+    <t>open_criminal_case</t>
+  </si>
+  <si>
+    <t>Открытое уголовное дело</t>
+  </si>
+  <si>
+    <t>is_payment_sberconnect</t>
+  </si>
+  <si>
+    <t>Использовать выплату SberConnect+</t>
+  </si>
+  <si>
+    <t>payment_sberconnect_status</t>
+  </si>
+  <si>
+    <t>Статус выплаты по SberConnect+</t>
+  </si>
+  <si>
+    <t>comment_payment_sberconnect</t>
+  </si>
+  <si>
+    <t>Комментарий к выплате по SberConnect+</t>
+  </si>
+  <si>
+    <t>is_claims_control</t>
+  </si>
+  <si>
+    <t>Claims Control</t>
+  </si>
+  <si>
+    <t>d_curr_exchange</t>
+  </si>
+  <si>
+    <t>Дата курса</t>
+  </si>
+  <si>
+    <t>is_checked</t>
+  </si>
+  <si>
+    <t>Проверка пройдена</t>
+  </si>
+  <si>
+    <t>is_loss_not_fall_under_reins_term</t>
+  </si>
+  <si>
+    <t>Убыток не попадает под условия перестрахования</t>
+  </si>
+  <si>
+    <t>broker_inspection_id</t>
+  </si>
+  <si>
+    <t>id заявки, созданного в системе брокера</t>
+  </si>
+  <si>
+    <t>broker_inspection_data</t>
+  </si>
+  <si>
+    <t>Данные заявки от брокера</t>
+  </si>
+  <si>
+    <t>broker_name</t>
+  </si>
+  <si>
+    <t>Системное имя брокера</t>
+  </si>
+  <si>
+    <t>loss_exposure</t>
+  </si>
+  <si>
+    <t>Экспозиция по убытку</t>
+  </si>
+  <si>
+    <t>air_transport_type</t>
+  </si>
+  <si>
+    <t>Тип воздушного транспорта</t>
+  </si>
+  <si>
+    <t>cargo_departure_point</t>
+  </si>
+  <si>
+    <t>Точка отправления груза</t>
+  </si>
+  <si>
+    <t>trash_cargo_shipper_id</t>
+  </si>
+  <si>
+    <t>Отправитель груза (ссылка на bps_contractor.id)</t>
+  </si>
+  <si>
+    <t>trash_cargo_recipient_id</t>
+  </si>
+  <si>
+    <t>Получатель груза (ссылка на bps_contractor.id)</t>
+  </si>
+  <si>
+    <t>appeal_subject</t>
+  </si>
+  <si>
+    <t>Предмет обращения</t>
+  </si>
+  <si>
+    <t>rail_transport_type</t>
+  </si>
+  <si>
+    <t>Тип железнодорожного транспорта</t>
+  </si>
+  <si>
+    <t>cargo_cost</t>
+  </si>
+  <si>
+    <t>Стоимость груза</t>
+  </si>
+  <si>
+    <t>cargo_destinations</t>
+  </si>
+  <si>
+    <t>Точка назначения груза</t>
+  </si>
+  <si>
+    <t>state_support</t>
+  </si>
+  <si>
+    <t>Наличие господдержки</t>
+  </si>
+  <si>
+    <t>cargo_status</t>
+  </si>
+  <si>
+    <t>Состояние груза</t>
+  </si>
+  <si>
+    <t>trash_tk_document_num</t>
+  </si>
+  <si>
+    <t>Номер документа ТК</t>
+  </si>
+  <si>
+    <t>product_category</t>
+  </si>
+  <si>
+    <t>Категория товара</t>
+  </si>
+  <si>
+    <t>event_location</t>
+  </si>
+  <si>
+    <t>Список мест события</t>
+  </si>
+  <si>
+    <t>datetime_make_decision</t>
+  </si>
+  <si>
+    <t>Дата и время регистрации перехода</t>
+  </si>
+  <si>
+    <t>senior_group_id</t>
+  </si>
+  <si>
+    <t>Старший группы (ссылка на auth_user.id)</t>
+  </si>
+  <si>
+    <t>marketplace</t>
+  </si>
+  <si>
+    <t>Маркетплейс</t>
+  </si>
+  <si>
+    <t>additional_losses_parent_corporate_claim_id</t>
+  </si>
+  <si>
+    <t>Родительский corporate_claim для дополнительных убытков (ссылка на bps_corporate_claim.id)</t>
+  </si>
+  <si>
+    <t>basis_payment_compensation</t>
+  </si>
+  <si>
+    <t>Основание компенсации выплаты</t>
+  </si>
+  <si>
+    <t>unknown_bordero</t>
+  </si>
+  <si>
+    <t>Бордеро неизвестно</t>
+  </si>
+  <si>
+    <t>is_waiting_approve_bordero</t>
+  </si>
+  <si>
+    <t>Ожидание подтверждения бордеро</t>
+  </si>
+  <si>
+    <t>d_departure</t>
+  </si>
+  <si>
+    <t>Дата отправления</t>
+  </si>
+  <si>
+    <t>cargo_weight</t>
+  </si>
+  <si>
+    <t>Вес груза</t>
+  </si>
+  <si>
+    <t>d_arrival</t>
+  </si>
+  <si>
+    <t>Дата прибытия</t>
+  </si>
+  <si>
+    <t>insurance_section</t>
+  </si>
+  <si>
+    <t>Секция страхования</t>
+  </si>
+  <si>
+    <t>n_claim_tk</t>
+  </si>
+  <si>
+    <t>Номер претензии ТК</t>
+  </si>
+  <si>
+    <t>request_ins_tasks_id</t>
+  </si>
+  <si>
+    <t>Задачи по заявке на страхование (ссылка на bps_request_ins_task.id)</t>
+  </si>
+  <si>
+    <t>is_military_risk</t>
+  </si>
+  <si>
+    <t>Военные риски с господдержкой</t>
+  </si>
+  <si>
+    <t>d_case_fact</t>
+  </si>
+  <si>
+    <t>Дата события (факт)</t>
+  </si>
+  <si>
+    <t>trash_count_click_search_contracts_button</t>
+  </si>
+  <si>
+    <t>Счетчик нажатий на кнопку по поиску догворов</t>
+  </si>
+  <si>
+    <t>control_clause</t>
+  </si>
+  <si>
+    <t>Оговорка о контроле сверх:</t>
+  </si>
+  <si>
+    <t>termination_of_the_agreement</t>
+  </si>
+  <si>
+    <t>Прекращение действия договора</t>
+  </si>
+  <si>
+    <t>payments_percent</t>
+  </si>
+  <si>
+    <t>Процент выплаты</t>
+  </si>
+  <si>
+    <t>add_losses_comment</t>
+  </si>
+  <si>
+    <t>Комментарий по связанным убыткам</t>
+  </si>
+  <si>
+    <t>additional_losses_parent_damage_request_id</t>
+  </si>
+  <si>
+    <t>Родительский damage_request для дополнительных убытков (ссылка на bps_damage_request.id)</t>
+  </si>
+  <si>
+    <t>d_link_to_parent_add_loss</t>
+  </si>
+  <si>
+    <t>Дата и время привязки к другому убытку</t>
+  </si>
+  <si>
+    <t>is_confirmation_trade_turnover</t>
+  </si>
+  <si>
+    <t>Подтверждение товарооборота</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
+    <t>Сумма фрахта</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>netto_volume</t>
+  </si>
+  <si>
+    <t>Объем (нетто)</t>
+  </si>
+  <si>
+    <t>claim_text</t>
+  </si>
+  <si>
+    <t>Текст претензии</t>
+  </si>
+  <si>
+    <t>cargo_shipper</t>
+  </si>
+  <si>
+    <t>character varying(800)</t>
+  </si>
+  <si>
+    <t>Отправитель груза</t>
+  </si>
+  <si>
+    <t>cargo_recipient</t>
+  </si>
+  <si>
+    <t>Получатель груза</t>
+  </si>
+  <si>
+    <t>additional_loss_container_id</t>
+  </si>
+  <si>
+    <t>id контейнера</t>
+  </si>
+  <si>
+    <t>transportation_number</t>
+  </si>
+  <si>
+    <t>Номер перевозки</t>
+  </si>
+  <si>
+    <t>bank_warranty_number</t>
+  </si>
+  <si>
+    <t>Номер банковской гарантии</t>
+  </si>
+  <si>
+    <t>insured_event</t>
+  </si>
+  <si>
+    <t>Страховой случай</t>
+  </si>
+  <si>
+    <t>d_reimbursement_loss</t>
+  </si>
+  <si>
+    <t>Дата возмещения расходов по предотвращению убытка</t>
+  </si>
+  <si>
+    <t>committee_protocol</t>
+  </si>
+  <si>
+    <t>Протокол комитета</t>
+  </si>
+  <si>
+    <t>is_major_loss</t>
+  </si>
+  <si>
+    <t>Крупный убыток</t>
+  </si>
+  <si>
+    <t>vessel_type</t>
+  </si>
+  <si>
+    <t>Тип судна</t>
+  </si>
+  <si>
+    <t>gross_tonnage</t>
+  </si>
+  <si>
+    <t>Валовая вместимость</t>
+  </si>
+  <si>
+    <t>vessel_flag</t>
+  </si>
+  <si>
+    <t>Флаг судна</t>
+  </si>
+  <si>
+    <t>classification_society</t>
+  </si>
+  <si>
+    <t>Классификационное общество</t>
   </si>
 </sst>
 </file>
@@ -70863,7 +71991,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FA4A3C-67F5-4BB9-B776-B8D294646CD0}">
-  <dimension ref="A1:G585"/>
+  <dimension ref="A1:G810"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.1796875" bestFit="1" customWidth="1"/>
@@ -84328,6 +85456,5181 @@
       </c>
       <c r="G585" s="1" t="s">
         <v>1557</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A586" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C586">
+        <v>1</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F586" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G586" s="1" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A587" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C587">
+        <v>2</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E587" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F587" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G587" s="1" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A588" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C588">
+        <v>3</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F588" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G588" s="1" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A589" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C589">
+        <v>4</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E589" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F589" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G589" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A590" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C590">
+        <v>5</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E590" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F590" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G590" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A591" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C591">
+        <v>6</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F591" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G591" s="1" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A592" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C592">
+        <v>7</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E592" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F592" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G592" s="1" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A593" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C593">
+        <v>8</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F593" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G593" s="1" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A594" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C594">
+        <v>9</v>
+      </c>
+      <c r="D594" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F594" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G594" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A595" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C595">
+        <v>10</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F595" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G595" s="1" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A596" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C596">
+        <v>11</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G596" s="1" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A597" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C597">
+        <v>12</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F597" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A598" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C598">
+        <v>13</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F598" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A599" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C599">
+        <v>14</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F599" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A600" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C600">
+        <v>15</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F600" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G600" s="1" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A601" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C601">
+        <v>16</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G601" s="1" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A602" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C602">
+        <v>17</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F602" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G602" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A603" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C603">
+        <v>18</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F603" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G603" s="1" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A604" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C604">
+        <v>19</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F604" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G604" s="1" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A605" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C605">
+        <v>20</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A606" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C606">
+        <v>21</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G606" s="1" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A607" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C607">
+        <v>22</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F607" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G607" s="1" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A608" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C608">
+        <v>23</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F608" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G608" s="1" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A609" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C609">
+        <v>24</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F609" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G609" s="1" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A610" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C610">
+        <v>25</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G610" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A611" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C611">
+        <v>26</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F611" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G611" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A612" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C612">
+        <v>27</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F612" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G612" s="1" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A613" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C613">
+        <v>28</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G613" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A614" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C614">
+        <v>29</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F614" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G614" s="1" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A615" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C615">
+        <v>30</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F615" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G615" s="1" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A616" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C616">
+        <v>31</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G616" s="1" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A617" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C617">
+        <v>32</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F617" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A618" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C618">
+        <v>33</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F618" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G618" s="1" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A619" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C619">
+        <v>34</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>2458</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F619" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G619" s="1" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A620" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C620">
+        <v>35</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G620" s="1" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A621" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C621">
+        <v>36</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F621" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G621" s="1" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A622" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C622">
+        <v>37</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>2464</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F622" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G622" s="1" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A623" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C623">
+        <v>38</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G623" s="1" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A624" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C624">
+        <v>39</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G624" s="1" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A625" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C625">
+        <v>40</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F625" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G625" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A626" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C626">
+        <v>41</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>2470</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F626" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G626" s="1" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A627" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C627">
+        <v>42</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G627" s="1" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A628" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C628">
+        <v>43</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G628" s="1" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A629" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C629">
+        <v>44</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G629" s="1" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A630" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C630">
+        <v>45</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G630" s="1" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A631" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C631">
+        <v>46</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F631" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G631" s="1" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A632" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C632">
+        <v>47</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G632" s="1" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A633" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C633">
+        <v>48</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G633" s="1" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A634" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C634">
+        <v>49</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G634" s="1" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A635" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C635">
+        <v>50</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F635" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G635" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A636" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C636">
+        <v>51</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F636" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G636" s="1" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A637" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C637">
+        <v>52</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F637" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G637" s="1" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A638" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C638">
+        <v>53</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G638" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A639" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C639">
+        <v>54</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G639" s="1" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A640" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C640">
+        <v>55</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F640" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G640" s="1" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A641" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C641">
+        <v>56</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F641" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G641" s="1" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A642" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C642">
+        <v>57</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F642" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G642" s="1" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A643" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C643">
+        <v>58</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G643" s="1" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A644" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C644">
+        <v>59</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G644" s="1" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A645" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C645">
+        <v>60</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>2507</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G645" s="1" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A646" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C646">
+        <v>61</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G646" s="1" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A647" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C647">
+        <v>62</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>2511</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G647" s="1" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A648" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C648">
+        <v>63</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G648" s="1" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A649" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C649">
+        <v>64</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G649" s="1" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A650" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C650">
+        <v>65</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F650" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G650" s="1" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A651" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C651">
+        <v>66</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>2518</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F651" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G651" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A652" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C652">
+        <v>67</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>2520</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F652" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G652" s="1" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A653" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C653">
+        <v>68</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F653" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G653" s="1" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A654" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C654">
+        <v>69</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>2524</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F654" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G654" s="1" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A655" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C655">
+        <v>70</v>
+      </c>
+      <c r="D655" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F655" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G655" s="1" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A656" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C656">
+        <v>71</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>2528</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F656" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G656" s="1" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A657" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C657">
+        <v>72</v>
+      </c>
+      <c r="D657" s="1" t="s">
+        <v>2530</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F657" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G657" s="1" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A658" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C658">
+        <v>73</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F658" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G658" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A659" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C659">
+        <v>74</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>2533</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F659" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G659" s="1" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A660" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C660">
+        <v>75</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F660" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G660" s="1" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A661" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C661">
+        <v>76</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F661" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G661" s="1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A662" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C662">
+        <v>77</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F662" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G662" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A663" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C663">
+        <v>78</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F663" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G663" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A664" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C664">
+        <v>79</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F664" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G664" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A665" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C665">
+        <v>80</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F665" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G665" s="1" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A666" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C666">
+        <v>81</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F666" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G666" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A667" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C667">
+        <v>82</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F667" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G667" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A668" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C668">
+        <v>83</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F668" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G668" s="1" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A669" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C669">
+        <v>84</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F669" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G669" s="1" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A670" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C670">
+        <v>85</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F670" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G670" s="1" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A671" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C671">
+        <v>86</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G671" s="1" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A672" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C672">
+        <v>87</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F672" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G672" s="1" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A673" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C673">
+        <v>88</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F673" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G673" s="1" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A674" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C674">
+        <v>89</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F674" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G674" s="1" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A675" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C675">
+        <v>90</v>
+      </c>
+      <c r="D675" s="1" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F675" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G675" s="1" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A676" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C676">
+        <v>91</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>2560</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F676" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G676" s="1" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A677" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C677">
+        <v>92</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F677" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G677" s="1" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A678" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C678">
+        <v>93</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>2564</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F678" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G678" s="1" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="679" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A679" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C679">
+        <v>94</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F679" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G679" s="1" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A680" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C680">
+        <v>95</v>
+      </c>
+      <c r="D680" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F680" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G680" s="1" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A681" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C681">
+        <v>96</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F681" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G681" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A682" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C682">
+        <v>97</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G682" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A683" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C683">
+        <v>98</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F683" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G683" s="1" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="684" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A684" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C684">
+        <v>99</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F684" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G684" s="1" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="685" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A685" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C685">
+        <v>100</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F685" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G685" s="1" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="686" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A686" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C686">
+        <v>101</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F686" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G686" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A687" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C687">
+        <v>102</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F687" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G687" s="1" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A688" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C688">
+        <v>103</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>2578</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F688" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G688" s="1" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A689" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C689">
+        <v>104</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>2580</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F689" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G689" s="1" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A690" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C690">
+        <v>105</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F690" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G690" s="1" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A691" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C691">
+        <v>106</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F691" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G691" s="1" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A692" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C692">
+        <v>107</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F692" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G692" s="1" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A693" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C693">
+        <v>108</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G693" s="1" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A694" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C694">
+        <v>109</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F694" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G694" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A695" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C695">
+        <v>110</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>2591</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G695" s="1" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A696" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C696">
+        <v>111</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G696" s="1" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A697" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C697">
+        <v>112</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>2594</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G697" s="1" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A698" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C698">
+        <v>113</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F698" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G698" s="1" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A699" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C699">
+        <v>114</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>2596</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G699" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A700" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C700">
+        <v>115</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A701" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C701">
+        <v>116</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A702" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C702">
+        <v>117</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F702" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A703" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C703">
+        <v>118</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F703" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G703" s="1" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A704" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C704">
+        <v>119</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>2604</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F704" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G704" s="1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A705" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C705">
+        <v>120</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>2605</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F705" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G705" s="1" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A706" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C706">
+        <v>121</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F706" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G706" s="1" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A707" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C707">
+        <v>122</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>2609</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F707" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G707" s="1" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A708" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C708">
+        <v>123</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>2611</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F708" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G708" s="1" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A709" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C709">
+        <v>124</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F709" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G709" s="1" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A710" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C710">
+        <v>125</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>2614</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F710" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G710" s="1" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A711" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C711">
+        <v>126</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>2616</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F711" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G711" s="1" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A712" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C712">
+        <v>127</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F712" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G712" s="1" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A713" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C713">
+        <v>128</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F713" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G713" s="1" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A714" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C714">
+        <v>129</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F714" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G714" s="1" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A715" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C715">
+        <v>130</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>2621</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F715" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G715" s="1" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A716" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C716">
+        <v>131</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>2623</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>2624</v>
+      </c>
+      <c r="F716" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G716" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A717" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C717">
+        <v>132</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F717" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G717" s="1" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A718" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C718">
+        <v>133</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>2627</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F718" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G718" s="1" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A719" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C719">
+        <v>134</v>
+      </c>
+      <c r="D719" s="1" t="s">
+        <v>2629</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F719" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G719" s="1" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A720" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C720">
+        <v>135</v>
+      </c>
+      <c r="D720" s="1" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F720" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G720" s="1" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A721" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C721">
+        <v>136</v>
+      </c>
+      <c r="D721" s="1" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F721" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G721" s="1" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A722" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C722">
+        <v>144</v>
+      </c>
+      <c r="D722" s="1" t="s">
+        <v>2635</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F722" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G722" s="1" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A723" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C723">
+        <v>145</v>
+      </c>
+      <c r="D723" s="1" t="s">
+        <v>2637</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F723" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G723" s="1" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A724" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C724">
+        <v>146</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>2639</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F724" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G724" s="1" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A725" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C725">
+        <v>147</v>
+      </c>
+      <c r="D725" s="1" t="s">
+        <v>2641</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F725" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G725" s="1" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A726" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C726">
+        <v>148</v>
+      </c>
+      <c r="D726" s="1" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F726" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G726" s="1" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A727" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C727">
+        <v>149</v>
+      </c>
+      <c r="D727" s="1" t="s">
+        <v>2645</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G727" s="1" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A728" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C728">
+        <v>150</v>
+      </c>
+      <c r="D728" s="1" t="s">
+        <v>2647</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F728" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G728" s="1" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A729" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C729">
+        <v>151</v>
+      </c>
+      <c r="D729" s="1" t="s">
+        <v>2649</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F729" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G729" s="1" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A730" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C730">
+        <v>152</v>
+      </c>
+      <c r="D730" s="1" t="s">
+        <v>2651</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F730" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G730" s="1" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A731" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C731">
+        <v>153</v>
+      </c>
+      <c r="D731" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F731" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G731" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A732" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C732">
+        <v>154</v>
+      </c>
+      <c r="D732" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F732" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G732" s="1" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A733" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C733">
+        <v>155</v>
+      </c>
+      <c r="D733" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F733" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G733" s="1" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A734" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C734">
+        <v>156</v>
+      </c>
+      <c r="D734" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F734" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G734" s="1" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A735" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C735">
+        <v>157</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>2653</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F735" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G735" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A736" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C736">
+        <v>158</v>
+      </c>
+      <c r="D736" s="1" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F736" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G736" s="1" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A737" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C737">
+        <v>159</v>
+      </c>
+      <c r="D737" s="1" t="s">
+        <v>2656</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F737" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G737" s="1" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A738" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C738">
+        <v>160</v>
+      </c>
+      <c r="D738" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F738" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G738" s="1" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A739" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C739">
+        <v>161</v>
+      </c>
+      <c r="D739" s="1" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F739" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G739" s="1" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A740" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C740">
+        <v>162</v>
+      </c>
+      <c r="D740" s="1" t="s">
+        <v>2662</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F740" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G740" s="1" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A741" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C741">
+        <v>163</v>
+      </c>
+      <c r="D741" s="1" t="s">
+        <v>2664</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F741" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G741" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A742" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C742">
+        <v>164</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F742" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G742" s="1" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A743" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C743">
+        <v>165</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>2665</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F743" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G743" s="1" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A744" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C744">
+        <v>166</v>
+      </c>
+      <c r="D744" s="1" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F744" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G744" s="1" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A745" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C745">
+        <v>167</v>
+      </c>
+      <c r="D745" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F745" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G745" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A746" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C746">
+        <v>169</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F746" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G746" s="1" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A747" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C747">
+        <v>170</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F747" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G747" s="1" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A748" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C748">
+        <v>171</v>
+      </c>
+      <c r="D748" s="1" t="s">
+        <v>2673</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F748" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G748" s="1" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A749" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C749">
+        <v>172</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>2675</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F749" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G749" s="1" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A750" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C750">
+        <v>173</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F750" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G750" s="1" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A751" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C751">
+        <v>174</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F751" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G751" s="1" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A752" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C752">
+        <v>175</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>2681</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F752" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G752" s="1" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A753" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C753">
+        <v>176</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>2683</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F753" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G753" s="1" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="754" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A754" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C754">
+        <v>177</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F754" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G754" s="1" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A755" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C755">
+        <v>178</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>2687</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F755" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G755" s="1" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A756" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C756">
+        <v>179</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>2689</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F756" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G756" s="1" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A757" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C757">
+        <v>180</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>2691</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F757" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G757" s="1" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A758" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C758">
+        <v>181</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F758" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G758" s="1" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A759" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C759">
+        <v>182</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>2695</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F759" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G759" s="1" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A760" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C760">
+        <v>183</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F760" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G760" s="1" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A761" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C761">
+        <v>184</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F761" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G761" s="1" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="762" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A762" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C762">
+        <v>185</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>2701</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F762" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G762" s="1" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="763" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A763" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C763">
+        <v>186</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>2703</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F763" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G763" s="1" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="764" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A764" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C764">
+        <v>187</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>2705</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F764" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G764" s="1" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="765" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A765" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C765">
+        <v>188</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>2707</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F765" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G765" s="1" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="766" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A766" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C766">
+        <v>189</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F766" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G766" s="1" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="767" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A767" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C767">
+        <v>190</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F767" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G767" s="1" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="768" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A768" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C768">
+        <v>191</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>2713</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F768" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G768" s="1" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="769" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A769" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C769">
+        <v>192</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>2715</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F769" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G769" s="1" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A770" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C770">
+        <v>193</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>2717</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F770" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G770" s="1" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="771" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A771" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C771">
+        <v>194</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>2719</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F771" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G771" s="1" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="772" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A772" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C772">
+        <v>195</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>2721</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F772" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G772" s="1" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="773" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A773" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C773">
+        <v>196</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>2723</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F773" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G773" s="1" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="774" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A774" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C774">
+        <v>197</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F774" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G774" s="1" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="775" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A775" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C775">
+        <v>198</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F775" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G775" s="1" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="776" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A776" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C776">
+        <v>199</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F776" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G776" s="1" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="777" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A777" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C777">
+        <v>200</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>2731</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F777" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G777" s="1" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="778" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A778" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C778">
+        <v>201</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F778" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G778" s="1" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="779" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A779" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C779">
+        <v>202</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>2735</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F779" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G779" s="1" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="780" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A780" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C780">
+        <v>203</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>2737</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F780" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G780" s="1" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="781" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A781" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C781">
+        <v>204</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F781" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G781" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="782" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A782" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C782">
+        <v>205</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F782" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G782" s="1" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="783" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A783" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C783">
+        <v>206</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F783" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G783" s="1" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="784" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A784" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C784">
+        <v>207</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F784" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G784" s="1" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="785" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A785" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C785">
+        <v>208</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>2745</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F785" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G785" s="1" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="786" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A786" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C786">
+        <v>209</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F786" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G786" s="1" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="787" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A787" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C787">
+        <v>210</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>2749</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F787" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G787" s="1" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="788" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A788" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C788">
+        <v>211</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F788" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G788" s="1" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="789" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A789" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C789">
+        <v>212</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>2753</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F789" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G789" s="1" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="790" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A790" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C790">
+        <v>213</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F790" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G790" s="1" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="791" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A791" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C791">
+        <v>214</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>2757</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F791" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G791" s="1" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="792" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A792" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C792">
+        <v>215</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>2759</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F792" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G792" s="1" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A793" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C793">
+        <v>216</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>2761</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F793" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G793" s="1" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A794" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C794">
+        <v>217</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>2763</v>
+      </c>
+      <c r="E794" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F794" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G794" s="1" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="795" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A795" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C795">
+        <v>218</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>2765</v>
+      </c>
+      <c r="E795" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F795" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G795" s="1" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="796" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A796" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C796">
+        <v>219</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2767</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F796" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G796" s="1" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="797" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A797" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C797">
+        <v>220</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E797" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F797" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G797" s="1" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="798" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A798" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C798">
+        <v>221</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>2771</v>
+      </c>
+      <c r="E798" s="1" t="s">
+        <v>2772</v>
+      </c>
+      <c r="F798" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G798" s="1" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="799" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A799" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C799">
+        <v>222</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>2774</v>
+      </c>
+      <c r="E799" s="1" t="s">
+        <v>2772</v>
+      </c>
+      <c r="F799" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G799" s="1" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="800" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A800" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C800">
+        <v>223</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E800" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F800" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G800" s="1" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="801" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A801" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C801">
+        <v>224</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>2778</v>
+      </c>
+      <c r="E801" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F801" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G801" s="1" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="802" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A802" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C802">
+        <v>225</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>2780</v>
+      </c>
+      <c r="E802" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F802" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G802" s="1" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="803" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A803" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C803">
+        <v>226</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>2782</v>
+      </c>
+      <c r="E803" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F803" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G803" s="1" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="804" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A804" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C804">
+        <v>227</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>2784</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F804" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G804" s="1" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="805" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A805" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C805">
+        <v>228</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>2786</v>
+      </c>
+      <c r="E805" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F805" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G805" s="1" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="806" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A806" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C806">
+        <v>229</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E806" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F806" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G806" s="1" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="807" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A807" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C807">
+        <v>230</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E807" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F807" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G807" s="1" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="808" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A808" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C808">
+        <v>231</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>2792</v>
+      </c>
+      <c r="E808" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F808" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G808" s="1" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="809" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A809" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C809">
+        <v>232</v>
+      </c>
+      <c r="D809" s="1" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E809" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F809" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G809" s="1" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="810" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A810" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C810">
+        <v>233</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>2796</v>
+      </c>
+      <c r="E810" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F810" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G810" s="1" t="s">
+        <v>2797</v>
       </c>
     </row>
   </sheetData>
